--- a/artfynd/S 1534-2026 artfynd.xlsx
+++ b/artfynd/S 1534-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117592088</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113489845</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116167224</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116167225</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117592074</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117592075</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117592078</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117592087</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116167218</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116167248</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117592100</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116167220</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1941,6 +2006,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116167227</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2046,6 +2116,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116167228</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2151,6 +2226,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116167230</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2258,6 +2338,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117592083</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2355,6 +2440,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116167250</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2452,6 +2542,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116167236</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2549,6 +2644,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116167238</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2646,6 +2746,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116167240</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2743,6 +2848,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116167242</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2840,6 +2950,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116167243</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2937,6 +3052,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116167244</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3047,6 +3167,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116167429</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3157,6 +3282,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116167430</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3267,6 +3397,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116167432</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3364,6 +3499,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117592094</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3461,6 +3601,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117592095</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3558,6 +3703,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117592096</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3672,6 +3822,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117592254</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3782,6 +3937,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117592258</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3896,6 +4056,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117592259</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4006,6 +4171,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117592260</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4116,6 +4286,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117592261</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4213,8 +4388,50 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117592092</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>